--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130870802</v>
+        <v>130870828</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582715</v>
+        <v>583216</v>
       </c>
       <c r="R9" t="n">
-        <v>6959670</v>
+        <v>6959386</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1473,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130870828</v>
+        <v>130870802</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,34 +1607,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583216</v>
+        <v>582715</v>
       </c>
       <c r="R11" t="n">
-        <v>6959386</v>
+        <v>6959670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1675,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2010,32 +2010,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130870831</v>
+        <v>130870818</v>
       </c>
       <c r="B15" t="n">
-        <v>83089</v>
+        <v>92267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583209</v>
+        <v>583241</v>
       </c>
       <c r="R15" t="n">
-        <v>6959416</v>
+        <v>6959405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,32 +2107,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130870818</v>
+        <v>130870792</v>
       </c>
       <c r="B16" t="n">
-        <v>92267</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583241</v>
+        <v>583131</v>
       </c>
       <c r="R16" t="n">
-        <v>6959405</v>
+        <v>6959482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130870792</v>
+        <v>130870831</v>
       </c>
       <c r="B17" t="n">
-        <v>91808</v>
+        <v>83089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,21 +2215,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583131</v>
+        <v>583209</v>
       </c>
       <c r="R17" t="n">
-        <v>6959482</v>
+        <v>6959416</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130870823</v>
+        <v>130870795</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,34 +2312,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582529</v>
+        <v>583098</v>
       </c>
       <c r="R18" t="n">
-        <v>6959663</v>
+        <v>6959481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2403,45 +2411,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130870816</v>
+        <v>130870798</v>
       </c>
       <c r="B19" t="n">
-        <v>80377</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582711</v>
+        <v>582557</v>
       </c>
       <c r="R19" t="n">
-        <v>6959664</v>
+        <v>6959519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2500,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130870795</v>
+        <v>130870797</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2533,7 +2554,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2543,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583098</v>
+        <v>582602</v>
       </c>
       <c r="R20" t="n">
-        <v>6959481</v>
+        <v>6959501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,7 +2604,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2610,53 +2631,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130870798</v>
+        <v>130870817</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>91819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582557</v>
+        <v>582663</v>
       </c>
       <c r="R21" t="n">
-        <v>6959519</v>
+        <v>6959537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2702,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,53 +2728,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130870797</v>
+        <v>130870816</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>80377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582602</v>
+        <v>582711</v>
       </c>
       <c r="R22" t="n">
-        <v>6959501</v>
+        <v>6959664</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,11 +2799,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,32 +2825,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130870817</v>
+        <v>130870823</v>
       </c>
       <c r="B23" t="n">
-        <v>91819</v>
+        <v>79243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2865,10 +2860,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582663</v>
+        <v>582529</v>
       </c>
       <c r="R23" t="n">
-        <v>6959537</v>
+        <v>6959663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,6 +2896,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130870803</v>
+        <v>130870820</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,42 +2938,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582704</v>
+        <v>583054</v>
       </c>
       <c r="R24" t="n">
-        <v>6959675</v>
+        <v>6959569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,11 +2998,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130870820</v>
+        <v>130870803</v>
       </c>
       <c r="B25" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,34 +3035,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583054</v>
+        <v>582704</v>
       </c>
       <c r="R25" t="n">
-        <v>6959569</v>
+        <v>6959675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3548,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130870827</v>
+        <v>130870794</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583142</v>
+        <v>583237</v>
       </c>
       <c r="R30" t="n">
-        <v>6959494</v>
+        <v>6959408</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130870804</v>
+        <v>130870827</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,42 +3656,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582667</v>
+        <v>583142</v>
       </c>
       <c r="R31" t="n">
-        <v>6959804</v>
+        <v>6959494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3724,11 +3716,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3755,7 +3742,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130870799</v>
+        <v>130870804</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -3788,7 +3775,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3798,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582540</v>
+        <v>582667</v>
       </c>
       <c r="R32" t="n">
-        <v>6959611</v>
+        <v>6959804</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3825,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall. Hela stammen full.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130870794</v>
+        <v>130870799</v>
       </c>
       <c r="B33" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3876,34 +3863,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583237</v>
+        <v>582540</v>
       </c>
       <c r="R33" t="n">
-        <v>6959408</v>
+        <v>6959611</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,6 +3931,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall. Hela stammen full.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130870810</v>
+        <v>130870791</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>91808</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,42 +4290,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582825</v>
+        <v>582769</v>
       </c>
       <c r="R37" t="n">
-        <v>6959676</v>
+        <v>6959516</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4358,11 +4350,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4389,7 +4376,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130870808</v>
+        <v>130870810</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4422,7 +4409,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4432,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582781</v>
+        <v>582825</v>
       </c>
       <c r="R38" t="n">
-        <v>6959717</v>
+        <v>6959676</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4472,7 +4459,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4499,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130870791</v>
+        <v>130870808</v>
       </c>
       <c r="B39" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4497,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582769</v>
+        <v>582781</v>
       </c>
       <c r="R39" t="n">
-        <v>6959516</v>
+        <v>6959717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,6 +4565,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130870819</v>
+        <v>130870805</v>
       </c>
       <c r="B2" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583057</v>
+        <v>582703</v>
       </c>
       <c r="R2" t="n">
-        <v>6959583</v>
+        <v>6959774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130870805</v>
+        <v>130870819</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582703</v>
+        <v>583057</v>
       </c>
       <c r="R3" t="n">
-        <v>6959774</v>
+        <v>6959583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130870828</v>
+        <v>130870802</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583216</v>
+        <v>582715</v>
       </c>
       <c r="R9" t="n">
-        <v>6959386</v>
+        <v>6959670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,6 +1481,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,7 +1512,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130870826</v>
+        <v>130870828</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1534,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582992</v>
+        <v>583216</v>
       </c>
       <c r="R10" t="n">
-        <v>6959624</v>
+        <v>6959386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130870802</v>
+        <v>130870826</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,42 +1620,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582715</v>
+        <v>582992</v>
       </c>
       <c r="R11" t="n">
-        <v>6959670</v>
+        <v>6959624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,11 +1680,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2301,53 +2301,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130870795</v>
+        <v>130870817</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>91819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583098</v>
+        <v>582663</v>
       </c>
       <c r="R18" t="n">
-        <v>6959481</v>
+        <v>6959537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,11 +2372,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2411,7 +2398,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130870798</v>
+        <v>130870797</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2454,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582557</v>
+        <v>582602</v>
       </c>
       <c r="R19" t="n">
-        <v>6959519</v>
+        <v>6959501</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2508,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130870797</v>
+        <v>130870795</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2554,7 +2541,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2564,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582602</v>
+        <v>583098</v>
       </c>
       <c r="R20" t="n">
-        <v>6959501</v>
+        <v>6959481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,7 +2591,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,45 +2618,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130870817</v>
+        <v>130870798</v>
       </c>
       <c r="B21" t="n">
-        <v>91819</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582663</v>
+        <v>582557</v>
       </c>
       <c r="R21" t="n">
-        <v>6959537</v>
+        <v>6959519</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,6 +2697,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130870816</v>
+        <v>130870823</v>
       </c>
       <c r="B22" t="n">
-        <v>80377</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582711</v>
+        <v>582529</v>
       </c>
       <c r="R22" t="n">
-        <v>6959664</v>
+        <v>6959663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,6 +2799,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,32 +2830,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130870823</v>
+        <v>130870816</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>80377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2860,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582529</v>
+        <v>582711</v>
       </c>
       <c r="R23" t="n">
-        <v>6959663</v>
+        <v>6959664</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,11 +2901,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130870820</v>
+        <v>130870803</v>
       </c>
       <c r="B24" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,34 +2938,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583054</v>
+        <v>582704</v>
       </c>
       <c r="R24" t="n">
-        <v>6959569</v>
+        <v>6959675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2998,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130870803</v>
+        <v>130870820</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,42 +3048,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582704</v>
+        <v>583054</v>
       </c>
       <c r="R25" t="n">
-        <v>6959675</v>
+        <v>6959569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3108,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130870825</v>
+        <v>130870815</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,34 +3255,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582799</v>
+        <v>583170</v>
       </c>
       <c r="R27" t="n">
-        <v>6959667</v>
+        <v>6959447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,6 +3323,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3341,7 +3354,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130870824</v>
+        <v>130870825</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3376,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582685</v>
+        <v>582799</v>
       </c>
       <c r="R28" t="n">
-        <v>6959786</v>
+        <v>6959667</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130870815</v>
+        <v>130870824</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,42 +3462,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583170</v>
+        <v>582685</v>
       </c>
       <c r="R29" t="n">
-        <v>6959447</v>
+        <v>6959786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,11 +3522,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3548,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130870794</v>
+        <v>130870827</v>
       </c>
       <c r="B30" t="n">
-        <v>91808</v>
+        <v>79243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583237</v>
+        <v>583142</v>
       </c>
       <c r="R30" t="n">
-        <v>6959408</v>
+        <v>6959494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130870827</v>
+        <v>130870794</v>
       </c>
       <c r="B31" t="n">
-        <v>79243</v>
+        <v>91808</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583142</v>
+        <v>583237</v>
       </c>
       <c r="R31" t="n">
-        <v>6959494</v>
+        <v>6959408</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,45 +3962,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130870832</v>
+        <v>130870812</v>
       </c>
       <c r="B34" t="n">
-        <v>80383</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583054</v>
+        <v>582898</v>
       </c>
       <c r="R34" t="n">
-        <v>6959568</v>
+        <v>6959678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,6 +4041,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,53 +4182,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870812</v>
+        <v>130870832</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80383</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582898</v>
+        <v>583054</v>
       </c>
       <c r="R36" t="n">
-        <v>6959678</v>
+        <v>6959568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,11 +4253,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130870805</v>
+        <v>130870819</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582703</v>
+        <v>583057</v>
       </c>
       <c r="R2" t="n">
-        <v>6959774</v>
+        <v>6959583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130870819</v>
+        <v>130870796</v>
       </c>
       <c r="B3" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583057</v>
+        <v>582707</v>
       </c>
       <c r="R3" t="n">
-        <v>6959583</v>
+        <v>6959492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130870796</v>
+        <v>130870805</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -915,7 +915,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582707</v>
+        <v>582703</v>
       </c>
       <c r="R4" t="n">
-        <v>6959492</v>
+        <v>6959774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130870821</v>
+        <v>130870801</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,30 +1113,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583201</v>
+        <v>582506</v>
       </c>
       <c r="R6" t="n">
-        <v>6959397</v>
+        <v>6959596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1181,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130870801</v>
+        <v>130870821</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,42 +1223,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582506</v>
+        <v>583201</v>
       </c>
       <c r="R7" t="n">
-        <v>6959596</v>
+        <v>6959397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1308,7 @@
         <v>130870830</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>130870828</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>130870826</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>130870829</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130870822</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>130870818</v>
       </c>
       <c r="B15" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>130870792</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>130870831</v>
       </c>
       <c r="B17" t="n">
-        <v>83089</v>
+        <v>83090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130870817</v>
+        <v>130870823</v>
       </c>
       <c r="B18" t="n">
-        <v>91819</v>
+        <v>79244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582663</v>
+        <v>582529</v>
       </c>
       <c r="R18" t="n">
-        <v>6959537</v>
+        <v>6959663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,6 +2372,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,53 +2403,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130870797</v>
+        <v>130870817</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>91820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582602</v>
+        <v>582663</v>
       </c>
       <c r="R19" t="n">
-        <v>6959501</v>
+        <v>6959537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,11 +2474,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,53 +2500,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130870795</v>
+        <v>130870816</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>80378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583098</v>
+        <v>582711</v>
       </c>
       <c r="R20" t="n">
-        <v>6959481</v>
+        <v>6959664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,11 +2571,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,7 +2597,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130870798</v>
+        <v>130870795</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2651,7 +2630,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2661,10 +2640,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582557</v>
+        <v>583098</v>
       </c>
       <c r="R21" t="n">
-        <v>6959519</v>
+        <v>6959481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,7 +2680,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,10 +2707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130870823</v>
+        <v>130870798</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,34 +2718,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582529</v>
+        <v>582557</v>
       </c>
       <c r="R22" t="n">
-        <v>6959663</v>
+        <v>6959519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,45 +2817,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130870816</v>
+        <v>130870797</v>
       </c>
       <c r="B23" t="n">
-        <v>80377</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582711</v>
+        <v>582602</v>
       </c>
       <c r="R23" t="n">
-        <v>6959664</v>
+        <v>6959501</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,6 +2896,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130870803</v>
+        <v>130870820</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,42 +2938,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582704</v>
+        <v>583054</v>
       </c>
       <c r="R24" t="n">
-        <v>6959675</v>
+        <v>6959569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,11 +2998,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130870820</v>
+        <v>130870803</v>
       </c>
       <c r="B25" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,34 +3035,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583054</v>
+        <v>582704</v>
       </c>
       <c r="R25" t="n">
-        <v>6959569</v>
+        <v>6959675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3244,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130870815</v>
+        <v>130870825</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,42 +3255,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583170</v>
+        <v>582799</v>
       </c>
       <c r="R27" t="n">
-        <v>6959447</v>
+        <v>6959667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3323,11 +3315,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3354,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130870825</v>
+        <v>130870824</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3389,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582799</v>
+        <v>582685</v>
       </c>
       <c r="R28" t="n">
-        <v>6959667</v>
+        <v>6959786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130870824</v>
+        <v>130870815</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3462,34 +3449,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582685</v>
+        <v>583170</v>
       </c>
       <c r="R29" t="n">
-        <v>6959786</v>
+        <v>6959447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3522,6 +3517,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3548,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130870827</v>
+        <v>130870794</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>91809</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583142</v>
+        <v>583237</v>
       </c>
       <c r="R30" t="n">
-        <v>6959494</v>
+        <v>6959408</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130870794</v>
+        <v>130870827</v>
       </c>
       <c r="B31" t="n">
-        <v>91808</v>
+        <v>79244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583237</v>
+        <v>583142</v>
       </c>
       <c r="R31" t="n">
-        <v>6959408</v>
+        <v>6959494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,53 +3962,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130870812</v>
+        <v>130870832</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>80384</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582898</v>
+        <v>583054</v>
       </c>
       <c r="R34" t="n">
-        <v>6959678</v>
+        <v>6959568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,11 +4033,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4182,45 +4169,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870832</v>
+        <v>130870812</v>
       </c>
       <c r="B36" t="n">
-        <v>80383</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583054</v>
+        <v>582898</v>
       </c>
       <c r="R36" t="n">
-        <v>6959568</v>
+        <v>6959678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,6 +4248,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130870791</v>
+        <v>130870810</v>
       </c>
       <c r="B37" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,34 +4290,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582769</v>
+        <v>582825</v>
       </c>
       <c r="R37" t="n">
-        <v>6959516</v>
+        <v>6959676</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4358,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4376,7 +4389,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130870810</v>
+        <v>130870808</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4409,7 +4422,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4419,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582825</v>
+        <v>582781</v>
       </c>
       <c r="R38" t="n">
-        <v>6959676</v>
+        <v>6959717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,7 +4472,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130870808</v>
+        <v>130870791</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4497,42 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582781</v>
+        <v>582769</v>
       </c>
       <c r="R39" t="n">
-        <v>6959717</v>
+        <v>6959516</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4565,11 +4570,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130870796</v>
+        <v>130870805</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -805,7 +805,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582707</v>
+        <v>582703</v>
       </c>
       <c r="R3" t="n">
-        <v>6959492</v>
+        <v>6959774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130870805</v>
+        <v>130870796</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -915,7 +915,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582703</v>
+        <v>582707</v>
       </c>
       <c r="R4" t="n">
-        <v>6959774</v>
+        <v>6959492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130870801</v>
+        <v>130870821</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,42 +1113,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582506</v>
+        <v>583201</v>
       </c>
       <c r="R6" t="n">
-        <v>6959596</v>
+        <v>6959397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130870821</v>
+        <v>130870801</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,30 +1206,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583201</v>
+        <v>582506</v>
       </c>
       <c r="R7" t="n">
-        <v>6959397</v>
+        <v>6959596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,6 +1274,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130870802</v>
+        <v>130870828</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582715</v>
+        <v>583216</v>
       </c>
       <c r="R9" t="n">
-        <v>6959670</v>
+        <v>6959386</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1473,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130870828</v>
+        <v>130870826</v>
       </c>
       <c r="B10" t="n">
         <v>79244</v>
@@ -1547,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583216</v>
+        <v>582992</v>
       </c>
       <c r="R10" t="n">
-        <v>6959386</v>
+        <v>6959624</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130870826</v>
+        <v>130870802</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,34 +1607,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582992</v>
+        <v>582715</v>
       </c>
       <c r="R11" t="n">
-        <v>6959624</v>
+        <v>6959670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1675,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3962,45 +3962,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130870832</v>
+        <v>130870811</v>
       </c>
       <c r="B34" t="n">
-        <v>80384</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583054</v>
+        <v>582879</v>
       </c>
       <c r="R34" t="n">
-        <v>6959568</v>
+        <v>6959670</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,6 +4041,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4059,7 +4072,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130870811</v>
+        <v>130870812</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4092,7 +4105,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4102,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582879</v>
+        <v>582898</v>
       </c>
       <c r="R35" t="n">
-        <v>6959670</v>
+        <v>6959678</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,7 +4155,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4169,53 +4182,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870812</v>
+        <v>130870832</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582898</v>
+        <v>583054</v>
       </c>
       <c r="R36" t="n">
-        <v>6959678</v>
+        <v>6959568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,11 +4253,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -2010,32 +2010,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130870818</v>
+        <v>130870792</v>
       </c>
       <c r="B15" t="n">
-        <v>92268</v>
+        <v>91809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583241</v>
+        <v>583131</v>
       </c>
       <c r="R15" t="n">
-        <v>6959405</v>
+        <v>6959482</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130870792</v>
+        <v>130870831</v>
       </c>
       <c r="B16" t="n">
-        <v>91809</v>
+        <v>83090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2118,21 +2118,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583131</v>
+        <v>583209</v>
       </c>
       <c r="R16" t="n">
-        <v>6959482</v>
+        <v>6959416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,32 +2204,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130870831</v>
+        <v>130870818</v>
       </c>
       <c r="B17" t="n">
-        <v>83090</v>
+        <v>92268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583209</v>
+        <v>583241</v>
       </c>
       <c r="R17" t="n">
-        <v>6959416</v>
+        <v>6959405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130870820</v>
+        <v>130870803</v>
       </c>
       <c r="B24" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,34 +2938,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583054</v>
+        <v>582704</v>
       </c>
       <c r="R24" t="n">
-        <v>6959569</v>
+        <v>6959675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2998,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130870803</v>
+        <v>130870820</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,42 +3048,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582704</v>
+        <v>583054</v>
       </c>
       <c r="R25" t="n">
-        <v>6959675</v>
+        <v>6959569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3103,11 +3108,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130870824</v>
+        <v>130870815</v>
       </c>
       <c r="B28" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,34 +3352,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582685</v>
+        <v>583170</v>
       </c>
       <c r="R28" t="n">
-        <v>6959786</v>
+        <v>6959447</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,6 +3420,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3438,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130870815</v>
+        <v>130870824</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,42 +3462,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583170</v>
+        <v>582685</v>
       </c>
       <c r="R29" t="n">
-        <v>6959447</v>
+        <v>6959786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,11 +3522,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,53 +3962,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130870811</v>
+        <v>130870832</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>80384</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582879</v>
+        <v>583054</v>
       </c>
       <c r="R34" t="n">
-        <v>6959670</v>
+        <v>6959568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,11 +4033,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4072,7 +4059,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130870812</v>
+        <v>130870811</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4105,7 +4092,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4115,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582898</v>
+        <v>582879</v>
       </c>
       <c r="R35" t="n">
-        <v>6959678</v>
+        <v>6959670</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,7 +4142,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4182,45 +4169,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870832</v>
+        <v>130870812</v>
       </c>
       <c r="B36" t="n">
-        <v>80384</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583054</v>
+        <v>582898</v>
       </c>
       <c r="R36" t="n">
-        <v>6959568</v>
+        <v>6959678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,6 +4248,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130870819</v>
+        <v>130870805</v>
       </c>
       <c r="B2" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583057</v>
+        <v>582703</v>
       </c>
       <c r="R2" t="n">
-        <v>6959583</v>
+        <v>6959774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130870805</v>
+        <v>130870796</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -805,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -815,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582703</v>
+        <v>582707</v>
       </c>
       <c r="R3" t="n">
-        <v>6959774</v>
+        <v>6959492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130870796</v>
+        <v>130870819</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,42 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582707</v>
+        <v>583057</v>
       </c>
       <c r="R4" t="n">
-        <v>6959492</v>
+        <v>6959583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130870826</v>
+        <v>130870802</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,34 +1510,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582992</v>
+        <v>582715</v>
       </c>
       <c r="R10" t="n">
-        <v>6959624</v>
+        <v>6959670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,6 +1578,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130870802</v>
+        <v>130870826</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,42 +1620,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582715</v>
+        <v>582992</v>
       </c>
       <c r="R11" t="n">
-        <v>6959670</v>
+        <v>6959624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,11 +1680,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2010,32 +2010,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130870792</v>
+        <v>130870818</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
+        <v>92268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583131</v>
+        <v>583241</v>
       </c>
       <c r="R15" t="n">
-        <v>6959482</v>
+        <v>6959405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130870831</v>
+        <v>130870792</v>
       </c>
       <c r="B16" t="n">
-        <v>83090</v>
+        <v>91809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2118,21 +2118,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583209</v>
+        <v>583131</v>
       </c>
       <c r="R16" t="n">
-        <v>6959416</v>
+        <v>6959482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,32 +2204,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130870818</v>
+        <v>130870831</v>
       </c>
       <c r="B17" t="n">
-        <v>92268</v>
+        <v>83090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583241</v>
+        <v>583209</v>
       </c>
       <c r="R17" t="n">
-        <v>6959405</v>
+        <v>6959416</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130870823</v>
+        <v>130870798</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,34 +2312,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582529</v>
+        <v>582557</v>
       </c>
       <c r="R18" t="n">
-        <v>6959663</v>
+        <v>6959519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2403,45 +2411,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130870817</v>
+        <v>130870797</v>
       </c>
       <c r="B19" t="n">
-        <v>91820</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582663</v>
+        <v>582602</v>
       </c>
       <c r="R19" t="n">
-        <v>6959537</v>
+        <v>6959501</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2597,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130870795</v>
+        <v>130870823</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,42 +2629,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583098</v>
+        <v>582529</v>
       </c>
       <c r="R21" t="n">
-        <v>6959481</v>
+        <v>6959663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,7 +2693,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2707,53 +2720,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130870798</v>
+        <v>130870817</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91820</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582557</v>
+        <v>582663</v>
       </c>
       <c r="R22" t="n">
-        <v>6959519</v>
+        <v>6959537</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,11 +2791,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130870797</v>
+        <v>130870795</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2850,7 +2850,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582602</v>
+        <v>583098</v>
       </c>
       <c r="R23" t="n">
-        <v>6959501</v>
+        <v>6959481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130870815</v>
+        <v>130870824</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,42 +3352,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583170</v>
+        <v>582685</v>
       </c>
       <c r="R28" t="n">
-        <v>6959447</v>
+        <v>6959786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3420,11 +3412,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3451,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130870824</v>
+        <v>130870815</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3462,34 +3449,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582685</v>
+        <v>583170</v>
       </c>
       <c r="R29" t="n">
-        <v>6959786</v>
+        <v>6959447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3522,6 +3517,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3548,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130870794</v>
+        <v>130870827</v>
       </c>
       <c r="B30" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583237</v>
+        <v>583142</v>
       </c>
       <c r="R30" t="n">
-        <v>6959408</v>
+        <v>6959494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130870827</v>
+        <v>130870794</v>
       </c>
       <c r="B31" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583142</v>
+        <v>583237</v>
       </c>
       <c r="R31" t="n">
-        <v>6959494</v>
+        <v>6959408</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,45 +3962,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130870832</v>
+        <v>130870812</v>
       </c>
       <c r="B34" t="n">
-        <v>80384</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583054</v>
+        <v>582898</v>
       </c>
       <c r="R34" t="n">
-        <v>6959568</v>
+        <v>6959678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,6 +4041,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4059,53 +4072,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130870811</v>
+        <v>130870832</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>80384</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582879</v>
+        <v>583054</v>
       </c>
       <c r="R35" t="n">
-        <v>6959670</v>
+        <v>6959568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,11 +4143,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4169,7 +4169,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870812</v>
+        <v>130870811</v>
       </c>
       <c r="B36" t="n">
         <v>57884</v>
@@ -4202,7 +4202,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582898</v>
+        <v>582879</v>
       </c>
       <c r="R36" t="n">
-        <v>6959678</v>
+        <v>6959670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130870810</v>
+        <v>130870791</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,42 +4290,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582825</v>
+        <v>582769</v>
       </c>
       <c r="R37" t="n">
-        <v>6959676</v>
+        <v>6959516</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4358,11 +4350,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4389,7 +4376,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130870808</v>
+        <v>130870810</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4422,7 +4409,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4432,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582781</v>
+        <v>582825</v>
       </c>
       <c r="R38" t="n">
-        <v>6959717</v>
+        <v>6959676</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4472,7 +4459,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4499,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130870791</v>
+        <v>130870808</v>
       </c>
       <c r="B39" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4497,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582769</v>
+        <v>582781</v>
       </c>
       <c r="R39" t="n">
-        <v>6959516</v>
+        <v>6959717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,6 +4565,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 62375-2025 artfynd.xlsx
+++ b/artfynd/A 62375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130870805</v>
+        <v>130870819</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582703</v>
+        <v>583057</v>
       </c>
       <c r="R2" t="n">
-        <v>6959774</v>
+        <v>6959583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130870796</v>
+        <v>130870805</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -818,7 +805,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582707</v>
+        <v>582703</v>
       </c>
       <c r="R3" t="n">
-        <v>6959492</v>
+        <v>6959774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130870819</v>
+        <v>130870796</v>
       </c>
       <c r="B4" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,34 +893,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583057</v>
+        <v>582707</v>
       </c>
       <c r="R4" t="n">
-        <v>6959583</v>
+        <v>6959492</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,6 +961,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130870802</v>
+        <v>130870826</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,42 +1510,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582715</v>
+        <v>582992</v>
       </c>
       <c r="R10" t="n">
-        <v>6959670</v>
+        <v>6959624</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,11 +1570,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130870826</v>
+        <v>130870802</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,34 +1607,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582992</v>
+        <v>582715</v>
       </c>
       <c r="R11" t="n">
-        <v>6959624</v>
+        <v>6959670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1675,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130870798</v>
+        <v>130870823</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,42 +2312,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582557</v>
+        <v>582529</v>
       </c>
       <c r="R18" t="n">
-        <v>6959519</v>
+        <v>6959663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,7 +2376,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2411,53 +2403,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130870797</v>
+        <v>130870816</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>80378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582602</v>
+        <v>582711</v>
       </c>
       <c r="R19" t="n">
-        <v>6959501</v>
+        <v>6959664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2474,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,10 +2500,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130870816</v>
+        <v>130870817</v>
       </c>
       <c r="B20" t="n">
-        <v>80378</v>
+        <v>91820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2511,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2535,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582711</v>
+        <v>582663</v>
       </c>
       <c r="R20" t="n">
-        <v>6959664</v>
+        <v>6959537</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2597,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130870823</v>
+        <v>130870797</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,34 +2608,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582529</v>
+        <v>582602</v>
       </c>
       <c r="R21" t="n">
-        <v>6959663</v>
+        <v>6959501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,7 +2680,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,45 +2707,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130870817</v>
+        <v>130870795</v>
       </c>
       <c r="B22" t="n">
-        <v>91820</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582663</v>
+        <v>583098</v>
       </c>
       <c r="R22" t="n">
-        <v>6959537</v>
+        <v>6959481</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,6 +2786,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130870795</v>
+        <v>130870798</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2850,7 +2850,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583098</v>
+        <v>582557</v>
       </c>
       <c r="R23" t="n">
-        <v>6959481</v>
+        <v>6959519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130870803</v>
+        <v>130870820</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,42 +2938,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582704</v>
+        <v>583054</v>
       </c>
       <c r="R24" t="n">
-        <v>6959675</v>
+        <v>6959569</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,11 +2998,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130870820</v>
+        <v>130870803</v>
       </c>
       <c r="B25" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,34 +3035,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583054</v>
+        <v>582704</v>
       </c>
       <c r="R25" t="n">
-        <v>6959569</v>
+        <v>6959675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,6 +3103,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3548,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130870827</v>
+        <v>130870799</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,34 +3559,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583142</v>
+        <v>582540</v>
       </c>
       <c r="R30" t="n">
-        <v>6959494</v>
+        <v>6959611</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,6 +3627,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall. Hela stammen full.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3645,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130870794</v>
+        <v>130870804</v>
       </c>
       <c r="B31" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,34 +3669,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583237</v>
+        <v>582667</v>
       </c>
       <c r="R31" t="n">
-        <v>6959408</v>
+        <v>6959804</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,6 +3737,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3742,10 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130870804</v>
+        <v>130870827</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,42 +3779,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582667</v>
+        <v>583142</v>
       </c>
       <c r="R32" t="n">
-        <v>6959804</v>
+        <v>6959494</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3821,11 +3839,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3852,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130870799</v>
+        <v>130870794</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3863,42 +3876,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582540</v>
+        <v>583237</v>
       </c>
       <c r="R33" t="n">
-        <v>6959611</v>
+        <v>6959408</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3931,11 +3936,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall. Hela stammen full.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,45 +4072,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130870832</v>
+        <v>130870811</v>
       </c>
       <c r="B35" t="n">
-        <v>80384</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583054</v>
+        <v>582879</v>
       </c>
       <c r="R35" t="n">
-        <v>6959568</v>
+        <v>6959670</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,6 +4151,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4169,53 +4182,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130870811</v>
+        <v>130870832</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pålmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582879</v>
+        <v>583054</v>
       </c>
       <c r="R36" t="n">
-        <v>6959670</v>
+        <v>6959568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,11 +4253,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,7 +4376,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130870810</v>
+        <v>130870808</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4409,7 +4409,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582825</v>
+        <v>582781</v>
       </c>
       <c r="R38" t="n">
-        <v>6959676</v>
+        <v>6959717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,7 +4486,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130870808</v>
+        <v>130870810</v>
       </c>
       <c r="B39" t="n">
         <v>57884</v>
@@ -4519,7 +4519,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582781</v>
+        <v>582825</v>
       </c>
       <c r="R39" t="n">
-        <v>6959717</v>
+        <v>6959676</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
